--- a/Excel/Excel Workbook/NPV Example.xlsx
+++ b/Excel/Excel Workbook/NPV Example.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B05362-8981-4F25-A189-227DD17FDEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF8A23D-80B5-4528-98EB-292211CEEAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,6 +54,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;₦&quot;#,##0.00;[Red]\-&quot;₦&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -83,9 +86,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,6 +456,7 @@
       <c r="D9" t="s">
         <v>3</v>
       </c>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">

--- a/Excel/Excel Workbook/NPV Example.xlsx
+++ b/Excel/Excel Workbook/NPV Example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF8A23D-80B5-4528-98EB-292211CEEAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE5619C-74F9-4030-956E-0BE6C90CFDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
